--- a/PEP8U_PHYSICS.xlsx
+++ b/PEP8U_PHYSICS.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="1461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2465" uniqueCount="1457">
   <si>
     <t>textbook_id</t>
   </si>
@@ -2894,7 +2894,7 @@
     <t>国际单位制（SI）</t>
   </si>
   <si>
-    <t>鉴于这种认识，国际计量组织制定了一套国际统一的单位，称之为国际单位制（SI） ，推荐各国使用。目前世界上大多数国家和地区已经采用国际单位制，我国的法定计量单位也是以国际单位制为基础制定的</t>
+    <t>鉴于这种认识，国际计量组织制定了一套国际统一的单位，称之为国际单位制（SI），推荐各国使用。目前世界上大多数国家和地区已经采用国际单位制，我国的法定计量单位也是以国际单位制为基础制定的。</t>
   </si>
   <si>
     <t>T08-01-03;T02-02-01;T06-02-01</t>
@@ -2960,7 +2960,7 @@
     <t>汽车倒车防撞、智能机器人</t>
   </si>
   <si>
-    <t>超声波在空气中的传播速度约为 340 m/s，它具有指向性好、反射能力强、能量集中等特点，因而经常被用于距离的测量、汽车倒车防撞、智能机器人等领域。 超声波测距的原理如图 1.4-4 所示</t>
+    <t>超声波在空气中的传播速度约为 340 m/s，它具有指向性好、反射能力强、能量集中等特点，因而经常被用于距离的测量、汽车倒车防撞、智能机器人等领域。 超声波测距的原理如图 1.4-4 所示。</t>
   </si>
   <si>
     <t>T06-04-01</t>
@@ -2975,7 +2975,7 @@
     <t>骨传导不用空气传声</t>
   </si>
   <si>
-    <t>骨传导不用空气传声，可以有效避免嘈杂环境的干扰，常应用在工业、战场等特殊场合中。而利用骨传导原理制成的助听器、耳机等更是在生活中得到了广泛的应用</t>
+    <t>骨传导不用空气传声，可以有效避免嘈杂环境的干扰，常应用在工业、战场等特殊场合中。而利用骨传导原理制成的助听器、耳机等更是在生活中得到了广泛的应用。</t>
   </si>
   <si>
     <t>T05-01-01</t>
@@ -2999,7 +2999,7 @@
     <t>贾湖骨笛</t>
   </si>
   <si>
-    <t>在河南舞阳出土的 8000 多年前的贾湖骨笛，可以吹奏出七声音阶，是我国迄今发现的最早的管乐器（图 2.2-6） 。单簧管、 双簧管和各种号也是常见的管乐器</t>
+    <t>在河南舞阳出土的 8000 多年前的贾湖骨笛，可以吹奏出七声音阶，是我国迄今发现的最早的管乐器（图 2.2-6） 。单簧管、 双簧管和各种号也是常见的管乐器。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_02_02_02</t>
@@ -3011,7 +3011,7 @@
     <t>用自己制作的乐器进行演奏</t>
   </si>
   <si>
-    <t>在班里举行的小型音乐会上，用自己制作的乐器进行演奏，看看谁的乐器有新意，谁演奏得好。写出你的制作过程，看看以下制作方案能否给你启发</t>
+    <t>在班里举行的小型音乐会上，用自己制作的乐器进行演奏，看看谁的乐器有新意，谁演奏得好。写出你的制作过程，看看以下制作方案能否给你启发。</t>
   </si>
   <si>
     <t>T06-02-01;T06-01-03</t>
@@ -3026,7 +3026,7 @@
     <t>超声波检测技术应用很广</t>
   </si>
   <si>
-    <t>在生产实践中，超声波检测技术应用很广。例如，利用超声波可以检测出锅炉有没有裂纹，甚至还可以知道裂纹有多大、多深</t>
+    <t>在生产实践中，超声波检测技术应用很广。例如，利用超声波可以检测出锅炉有没有裂纹，甚至还可以知道裂纹有多大、多深。</t>
   </si>
   <si>
     <t>T03-03-03;T06-04-01</t>
@@ -3041,7 +3041,7 @@
     <t>我国古代高水平的建筑声学成就</t>
   </si>
   <si>
-    <t>圜丘等建筑反映出我国古代高水平的建筑声学成就。现在，人们也经常在设 计礼堂、音乐厅（图 2.3-10）等建筑时进行特别的声学设计，使听众听到的声音 更加饱满、悦耳</t>
+    <t>圜丘等建筑反映出我国古代高水平的建筑声学成就。现在，人们也经常在设计礼堂、音乐厅（。图 2.3-10）等建筑时进行特别的声学设计，使听众听到的声音更加饱满、悦耳</t>
   </si>
   <si>
     <t>T04-01-01;T06-04-01</t>
@@ -3056,7 +3056,7 @@
     <t>我国有些地方修筑了“音乐公路”</t>
   </si>
   <si>
-    <t>我国有些地方修筑了“音乐公路” 。当汽车以一 定速度匀速行驶时，就会奏出一段悦耳的乐曲</t>
+    <t>我国有些地方修筑了“音乐公路” 。当汽车以一 定速度匀速行驶时，就会奏出一段悦耳的乐曲。</t>
   </si>
   <si>
     <t>T06-04-01;T06-02-01</t>
@@ -3071,7 +3071,7 @@
     <t>长期生活在 90 dB 以上</t>
   </si>
   <si>
-    <t>长期生活在 90 dB 以上的噪声 环境中，听力会受到严重影响并产生神经衰弱、头疼、 高血压等疾病；如果突然暴露在高达 150 dB 的噪声环 境中，鼓膜会破裂出血，双耳完全失去听力</t>
+    <t>长期生活在 90 dB 以上的噪声环境中，听力会受到严重影响并产生神经衰弱、头疼、 高血压等疾病；如果突然暴露在高达 150 dB 的噪声环境中，鼓膜会破裂出血，双耳完全失去听力。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_02_04_02</t>
@@ -3080,7 +3080,7 @@
     <t>现代的城市把控制噪声列为环境保护</t>
   </si>
   <si>
-    <t>现代的城市把控制噪声列为环境保护的重要项目之一。 在需要安静环境的医院、学校和科学研究部门附近，常 常有禁止鸣喇叭的标志（图 2.4-3）</t>
+    <t>现代的城市把控制噪声列为环境保护的重要项目之一。 在需要安静环境的医院、学校和科学研究部门附近，常常有禁止鸣喇叭的标志（图 2.4-3）。</t>
   </si>
   <si>
     <t>T02-02-01</t>
@@ -3110,7 +3110,7 @@
     <t>材料是否易得、安全和环保</t>
   </si>
   <si>
-    <t>展示交流 1. 展示你制作的隔音房间模型（图 2.5-2） ，并从 隔音性能，空间占用率，材料是否易得、安全和环保等 方面对模型进行评价。 2. 相互交流，总结经验并进行反思，尝试对制作 的模型进行改进</t>
+    <t>展示交流 1. 展示你制作的隔音房间模型（图 2.5-2） ，并从隔音性能，空间占用率，材料是否易得、安全和环保等方面对模型进行评价。 2. 相互交流，总结经验并进行反思，尝试对制作的模型进行改进。</t>
   </si>
   <si>
     <t>T06-01-03;T06-04-01;T10-02-03</t>
@@ -3125,7 +3125,7 @@
     <t>为了做到不打扰他人</t>
   </si>
   <si>
-    <t>如果有了真正的隔音房间，为了做到不打扰他 人，也为了自己听力的健康，在使用时还要注意哪些  问题？</t>
+    <t>如果有了真正的隔音房间，为了做到不打扰他人，也为了自己听力的健康，在使用时还要注意哪些问题？</t>
   </si>
   <si>
     <t>T02-02-01;T05-01-01</t>
@@ -3140,7 +3140,7 @@
     <t>分别测量冰箱的冷藏室和冷冻室</t>
   </si>
   <si>
-    <t>请你选择合适的温度计，分别测量冰箱的冷藏室和冷冻室中不同位 置的温度，看看不同的食物适合放在冰箱的什么位置。 各种各样的温度计 人们为了判断身体是否发热，常常会测量体 温</t>
+    <t>请你选择合适的温度计，分别测量冰箱的冷藏室和冷冻室中不同位置的温度，看看不同的食物适合放在冰箱的什么位置。 各种各样的温度计人们为了判断身体是否发热，常常会测量体温</t>
   </si>
   <si>
     <t>T05-01-01;T02-02-01</t>
@@ -3155,7 +3155,7 @@
     <t>电子体温计</t>
   </si>
   <si>
-    <t>现在的电子体温计通过液晶屏可以直接显 示体温（图 3.1-6）。 无论是玻璃体温计还是电子体温计，都要接触 人体，并需要一定的测量时间</t>
+    <t>现在的电子体温计通过液晶屏可以直接显示体温（图 3.1-6）。 无论是玻璃体温计还是电子体温计，都要接触人体，并需要一定的测量时间。</t>
   </si>
   <si>
     <t>T05-01-01;T06-04-01</t>
@@ -3173,18 +3173,6 @@
     <t>工业生产中常将钢水铸造成有一定形状的工件（图 3.2-1）。钢水在变成工件的过程中，它的状态发生了怎样的变化？在状态变化的过程中，钢水吸热还是放热？</t>
   </si>
   <si>
-    <t>EV_PEP8U_PHYSICS_03_02_02</t>
-  </si>
-  <si>
-    <t>注意避免烫伤</t>
-  </si>
-  <si>
-    <t>T02-02-01;T06-02-01;T02-03-03</t>
-  </si>
-  <si>
-    <t>公共责任;证据推理;国防与国家安全意识</t>
-  </si>
-  <si>
     <t>EV_PEP8U_PHYSICS_03_02_03</t>
   </si>
   <si>
@@ -3200,7 +3188,7 @@
     <t>正确读取和记录实验数据</t>
   </si>
   <si>
-    <t>证据 根据对问题的猜 想 ，设计实验方案 ， 选用相应的实验器材 进行实验 ，正确读取 和记录实验数据 。实 验数据是科学探究的 重要证据</t>
+    <t>证据 根据对问题的猜想，设计实验方案，选用相应的实验器材进行实验 ，正确读取和记录实验数据。实验数据是科学探究的重要证据。</t>
   </si>
   <si>
     <t>T06-02-01;T02-02-01</t>
@@ -3215,7 +3203,7 @@
     <t>水蒸气引起的烫伤</t>
   </si>
   <si>
-    <t>烧水、做饭的时候，水蒸气引起的烫伤往往比开水 烫伤更严重，这是因为水蒸气和开水的温度虽然差不 多，但是水蒸气液化的时候还要放出大量的热</t>
+    <t>烧水、做饭的时候，水蒸气引起的烫伤往往比开水烫伤更严重，这是因为水蒸气和开水的温度虽然差不多，但是水蒸气液化的时候还要放出大量的热。</t>
   </si>
   <si>
     <t>T05-01-01;T02-03-03</t>
@@ -3230,7 +3218,7 @@
     <t>我国的青藏铁路</t>
   </si>
   <si>
-    <t>我国的青藏铁路是世界上海拔最高的铁路。铁 路穿过多年冻土区时，为了减小冻土因融化对路基 产生的影响，需要使冻土保持低温</t>
+    <t>我国的青藏铁路是世界上海拔最高的铁路。铁路穿过多年冻土区时，为了减小冻土因融化对路基产生的影响，需要使冻土保持低温。</t>
   </si>
   <si>
     <t>T02-01-01;T06-04-01</t>
@@ -3245,7 +3233,7 @@
     <t>共同保卫我们的蓝色家园</t>
   </si>
   <si>
-    <t>因此，我们不仅需要改 进节水技术（图 3.4-5） 、优化用水 系统的运行，更需要每个人提高节 水意识、养成良好的用水习惯，共 同保卫我们的蓝色家园</t>
+    <t>因此，我们不仅需要改进节水技术（图 3.4-5）、优化用水系统的运行，更需要每个人提高节水意识、养成良好的用水习惯，共同保卫我们的蓝色家园。</t>
   </si>
   <si>
     <t>T10-02-03</t>
@@ -3260,7 +3248,7 @@
     <t>造成水资源的浪费</t>
   </si>
   <si>
-    <t>生活中，有很多情况会造成水资源的浪费。比如，水龙头漏水，用水后水龙头 未关紧，用水不节制等</t>
+    <t>生活中，有很多情况会造成水资源的浪费。比如，水龙头漏水，用水后水龙头未关紧，用水不节制等。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_03_05_01</t>
@@ -3269,7 +3257,7 @@
     <t>优化烹饪过程或解决安全隐患</t>
   </si>
   <si>
-    <t>进 一步说明这些建议是怎样优化烹饪过程或解决安全隐患 的，并解释这些建议的科学依据。还可以撰写一篇观察 报告，从物理学的视角分析物态变化规律在烹饪过程中 所起的作用，总结认识体会</t>
+    <t>进一步说明这些建议是怎样优化烹饪过程或解决安全隐患的，并解释这些建议的科学依据。还可以撰写一篇观察报告，从物理学的视角分析物态变化规律在烹饪过程中所起的作用，总结认识体会。</t>
   </si>
   <si>
     <t>T02-03-03</t>
@@ -3284,7 +3272,7 @@
     <t>在家中实验前</t>
   </si>
   <si>
-    <t>在家中实验前， 请 确保 你处于安全 的操作环境中 ，并 能正确使用各种厨 具 ，家中还应有成 年人在场 ，操作时 须注意避免烫伤！</t>
+    <t>在家中实验前， 请确保你处于安全的操作环境中 ，并能正确使用各种厨具 ，家中还应有成年人在场 ，操作时须注意避免烫伤！</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_04_01_01</t>
@@ -3302,7 +3290,7 @@
     <t>造成“光污染”</t>
   </si>
   <si>
-    <t>当强烈的太阳光照射到这些光 滑的表面时，就会发生镜面反射，炫目的光干扰人们的 正常生活，造成“光污染”</t>
+    <t>当强烈的太阳光照射到这些光滑的表面时，就会发生镜面反射，炫目的光干扰人们的正常生活，造成“光污染”。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_04_02_02</t>
@@ -3311,16 +3299,16 @@
     <t>激光测距技术广泛应用</t>
   </si>
   <si>
-    <t>激光测距技术广泛应用在人造地球卫星测控、大地 测量等方面。例如，激光测距仪向目标天体发射激 光束，并接收反射回来的激光束，测出激光往返所 用的时间，就可以算出所测天体与地球之间的距离</t>
+    <t>激光测距技术广泛应用在人造地球卫星测控、大地测量等方面。例如，激光测距仪向目标天体发射激光束，并接收反射回来的激光束，测出激光往返所用的时间，就可以算出所测天体与地球之间的距离。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_04_03_01</t>
   </si>
   <si>
-    <t>古代人们就用磨光</t>
-  </si>
-  <si>
-    <t>平面镜的应用 平面镜的使用历史悠久，古代人们就用磨光 的铜面作为镜子（图 4.3-4）</t>
+    <t>古代人们就用磨光的铜面作为镜子</t>
+  </si>
+  <si>
+    <t>平面镜的应用 平面镜的使用历史悠久，古代人们就用磨光的铜面作为镜子（图 4.3-4）。</t>
   </si>
   <si>
     <t>T04-01-01;T06-02-01</t>
@@ -3335,7 +3323,7 @@
     <t>既节省燃料，又不污染环境</t>
   </si>
   <si>
-    <t>利用凹面镜制成的太阳灶（图 4.3-8） 可以会聚太阳光用来烧水、煮饭，既节省 燃料，又不污染环境。凹面镜的面积越 大，会聚的太阳光越多，温度也就越高</t>
+    <t>利用凹面镜制成的太阳灶（图 4.3-8） 可以会聚太阳光用来烧水、煮饭，既节省燃料，又不污染环境。凹面镜的面积越大，会聚的太阳光越多，温度也就越高。</t>
   </si>
   <si>
     <t>T10-02-03;T06-04-01</t>
@@ -3350,16 +3338,16 @@
     <t>京剧被列入我国第一批国家级非物质文化遗产</t>
   </si>
   <si>
-    <t>京剧被列入我国第一批国家级非物质文化遗产名 录。请在图 4.3-9 中分别画出京剧演员通过平面镜 看到的 A 点和 B 点的像</t>
+    <t>京剧被列入我国第一批国家级非物质文化遗产名录。请在图 4.3-9 中分别画出京剧演员通过平面镜看到的 A 点和 B 点的像。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_04_04_01</t>
   </si>
   <si>
-    <t>《梦溪笔谈》</t>
-  </si>
-  <si>
-    <t>《梦溪笔谈》中都有关于海市蜃楼的记载，宋代大诗人 苏轼在《登州海市》诗中也描述过海市蜃楼的奇观。可见，海市蜃楼是一种不算 少见的自然现象</t>
+    <t>《梦溪笔谈》和苏轼</t>
+  </si>
+  <si>
+    <t>《梦溪笔谈》中都有关于海市蜃楼的记载，宋代大诗人苏轼在《登州海市》诗中也描述过海市蜃楼的奇观。可见，海市蜃楼是一种不算少见的自然现象。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_04_05_01</t>
@@ -3368,7 +3356,7 @@
     <t>英国物理学家牛顿用玻璃三棱镜</t>
   </si>
   <si>
-    <t>直到 1666 年，英国物理学家牛顿用玻璃三棱镜分解了太阳 光，这才揭开了光的颜色之谜。  色散 人们早就学会将金刚石、水晶打磨成各种饰品</t>
+    <t>直到 1666 年，英国物理学家牛顿用玻璃三棱镜分解了太阳光，这才揭开了光的颜色之谜。  色散人们早就学会将金刚石、水晶打磨成各种饰品。</t>
   </si>
   <si>
     <t>T06-02-01;T04-01-01</t>
@@ -3383,7 +3371,7 @@
     <t>有助于诊断疾病</t>
   </si>
   <si>
-    <t>人生病的时 候，局部皮肤的温度异常，利用红外相机给皮肤拍照并 与健康人的照片（图 4.5-6）对比，有助于诊断疾病。 夜间人的体温比野外草木、岩石的温度高，人体辐射的 红外线比它们强</t>
+    <t>人生病的时候，局部皮肤的温度异常，利用红外相机给皮肤拍照并与健康人的照片（图 4.5-6）对比，有助于诊断疾病。 夜间人的体温比野外草木、岩石的温度高，人体辐射的红外线比它们强。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_04_05_03</t>
@@ -3392,7 +3380,7 @@
     <t>紫外线灯</t>
   </si>
   <si>
-    <t>医院的手术室和病房里常配备紫外线灯 来灭菌，一些学校的餐厅也装有紫外线 灯，有的公交车也会采取紫外线灯封闭 照射的方式消毒（图 4.5-9） 。紫外线灯 一般会发出淡紫色的光</t>
+    <t>医院的手术室和病房里常配备紫外线灯来灭菌，一些学校的餐厅也装有紫外线灯，有的公交车也会采取紫外线灯封闭照射的方式消毒（图 4.5-9） 。紫外线灯一般会发出淡紫色的光。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_05_01_01</t>
@@ -3401,13 +3389,13 @@
     <t>《淮南万毕术》</t>
   </si>
   <si>
-    <t>《淮南万毕术》记载： “削冰令圆， 举以向日，以艾承其影，则火生。 ”这是利用冰透 镜对日聚焦取火的最早记载</t>
+    <t>《淮南万毕术》记载： “削冰令圆， 举以向日，以艾承其影，则火生。 ”这是利用冰透镜对日聚焦取火的最早记载。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_05_01_02</t>
   </si>
   <si>
-    <t>瓶装水引发的</t>
+    <t>瓶装水引发的火灾</t>
   </si>
   <si>
     <t>调查发现，火灾是由放在仪表盘 上方防滑垫上的瓶装水引发的。瓶装水是怎样引发火灾的？</t>
@@ -3434,7 +3422,7 @@
     <t>数码照相机用一种电荷耦合器件</t>
   </si>
   <si>
-    <t>现在生活中常使用数码照相机，数码照 相机用一种电荷耦合器件作为感光元件代替胶片。这种 电荷耦合器件能把光信号转换成电信号，从而更方便地 记录物体的像</t>
+    <t>现在生活中常使用数码照相机，数码照相机用一种电荷耦合器件作为感光元件代替胶片。这种电荷耦合器件能把光信号转换成电信号，从而更方便地记录物体的像。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_05_03_01</t>
@@ -3446,7 +3434,7 @@
     <t>与各小组共享测量的数据</t>
   </si>
   <si>
-    <t>每个 小组可以自己选择适当的物距，并与各小组共享测量的数据</t>
+    <t>每个小组可以自己选择适当的物距，并与各小组共享测量的数据。</t>
   </si>
   <si>
     <t>T06-01-03;T06-02-01</t>
@@ -3461,7 +3449,7 @@
     <t>形成近视眼的原因</t>
   </si>
   <si>
-    <t>形成近视眼的原因是晶状体太厚，折光能力太强，或者 眼球在前后方向上太长，因此来自远处某点的光会聚在 视网膜前，到达视网膜时已经不是一点而是一个模糊的 光斑了（图 5.4-3 甲） 。利用凹透镜能使光发散的特点， 在眼睛前面放一个合适的凹透镜，就能使来自远处物体 的光会聚在视网膜上（图 5.4-3 乙 ）</t>
+    <t>形成近视眼的原因是晶状体太厚，折光能力太强，或者眼球在前后方向上太长，因此来自远处某点的光会聚在视网膜前，到达视网膜时已经不是一点而是一个模糊的 光斑了（图 5.4-3 甲） 。利用凹透镜能使光发散的特点， 在眼睛前面放一个合适的凹透镜，就能使来自远处物体的光会聚在视网膜上（图 5.4-3 乙 ）。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_05_04_02</t>
@@ -3470,7 +3458,7 @@
     <t>全国爱眼日</t>
   </si>
   <si>
-    <t>6 月 6 日是全国爱眼日。根据你的观察和了解，生活中有哪些不当的用眼习惯会 导致近视？</t>
+    <t>6 月 6 日是全国爱眼日。根据你的观察和了解，生活中有哪些不当的用眼习惯会导致近视？</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_05_05_01</t>
@@ -3479,7 +3467,7 @@
     <t>同学之间相互评价</t>
   </si>
   <si>
-    <t>同学之间相互评价，比一比 谁的望远镜更完善</t>
+    <t>同学之间相互评价，比一比谁的望远镜更完善</t>
   </si>
   <si>
     <t>T06-01-03;T06-04-01</t>
@@ -3494,7 +3482,7 @@
     <t>确凿的证据支持了哥白尼</t>
   </si>
   <si>
-    <t>1609 年，伽利略用自制的望远镜观察天体（图 5.5-7） ，以确凿的证据支持了哥白尼的“日心说” 。 他还第一个观察到了木星的卫星、太阳黑子和月球 上的环形山</t>
+    <t>1609 年，伽利略用自制的望远镜观察天体（图 5.5-7） ，以确凿的证据支持了哥白尼的“日心说” 。 他还第一个观察到了木星的卫星、太阳黑子和月球上的环形山。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_05_05_03</t>
@@ -3503,7 +3491,7 @@
     <t>我国不仅古代在天文</t>
   </si>
   <si>
-    <t>我国不仅古代在天文 观测上取得了丰硕的成果， 在现代也对宇宙探索作出 了很大贡献 。 2009 年， 郭 守敬望远镜建成 ，并于 2011年启动光谱巡天任务， 成为世界上第一个获取光 谱数突破千万量级的望远 镜（图5.5-8）</t>
+    <t>我国不仅古代在天文观测上取得了丰硕的成果， 在现代也对宇宙探索作出了很大贡献 。 2009 年， 郭守敬望远镜建成 ，并于 2011年启动光谱巡天任务， 成为世界上第一个获取光谱数突破千万量级的望远镜（图5.5-8）。</t>
   </si>
   <si>
     <t>T04-01-01;T02-01-01</t>
@@ -3515,7 +3503,7 @@
     <t>EV_PEP8U_PHYSICS_05_05_04</t>
   </si>
   <si>
-    <t>2020年，中国天眼正式开放运行</t>
+    <t>2020年，中国天眼正式开放运行。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_06_01_01</t>
@@ -3524,7 +3512,7 @@
     <t>战国时期的天平</t>
   </si>
   <si>
-    <t>图 6.1-1 战国时期的天平</t>
+    <t>图 6.1-1 战国时期的天平。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_06_01_02</t>
@@ -3548,7 +3536,7 @@
     <t>第 26 届国际计量大会决定更新千克的定义</t>
   </si>
   <si>
-    <t>2018 年，第 26 届国际计量大会决定更新千克的定义，在 不使用具体实物的情况下定义了质量单位</t>
+    <t>2018 年，第 26 届国际计量大会决定更新千克的定义，在不使用具体实物的情况下定义了质量单位。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_06_02_01</t>
@@ -3557,7 +3545,7 @@
     <t>通过所作的图像</t>
   </si>
   <si>
-    <t>通过所作的图像，可以直观地 看到铝块的质量与体积的关系。你从中能得出什么结论？</t>
+    <t>通过所作的图像，可以直观地看到铝块的质量与体积的关系。你从中能得出什么结论？</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_06_02_02</t>
@@ -3566,7 +3554,7 @@
     <t>冬天对自来水管的保护</t>
   </si>
   <si>
-    <t>在我国的北方，冬天对自来水管的保护十分重要。如果保护不好，水管内的 水结了冰，不仅影响正常的生活用水，有时还会把水管冻裂，造成设备的损坏</t>
+    <t>在我国的北方，冬天对自来水管的保护十分重要。如果保护不好，水管内的水结了冰，不仅影响正常的生活用水，有时还会把水管冻裂，造成设备的损坏。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_06_03_01</t>
@@ -3575,7 +3563,7 @@
     <t>为了选出饱满的种粒</t>
   </si>
   <si>
-    <t>例如，为了选出饱满的种粒，可以配制适当密度的 盐水进行选种。将种粒浸没在盐水中并适当搅拌，静置 一段时间后，清除水面漂浮的空粒、瘪粒，就可以选出 较好的种子（图 6.3-1）</t>
+    <t>例如，为了选出饱满的种粒，可以配制适当密度的盐水进行选种。将种粒浸没在盐水中并适当搅拌，静置一段时间后，清除水面漂浮的空粒、瘪粒，就可以选出较好的种子（图 6.3-1）。</t>
   </si>
   <si>
     <t>T03-03-03</t>
@@ -3590,7 +3578,7 @@
     <t>虽经多次重复测量</t>
   </si>
   <si>
-    <t>虽经多次重复测量，但仍然存在这个令人奇怪的差异。 后来，他与化学家拉姆塞合作，于 1894 年在从空气中取得的氮里，分离出另 一种当时还不知道的气体——氩，这个谜才解开了</t>
+    <t>19世纪末，英国物理学家瑞利在精确测量各种气体的密度时，发现从空气中取得的氮的密度是1.257 2 kg/m3，而从氨中取得的氮的密度却是1.250 5 kg/m3。虽经多次重复测量，但仍然存在这个令人奇怪的差异。后来，他与化学家拉姆塞合作，于1894年在从空气中取得的氮里，分离出另一种当时还不知道的气体——氩，这个谜才解开了。原来，氩的密度较大，空气中的氮混有少量氩，它的密度就比从氨中取得的纯氮的密度稍大一点儿。</t>
   </si>
   <si>
     <t>T06-02-01;T06-01-03;T04-01-01</t>
@@ -3620,7 +3608,7 @@
     <t>海上风力发电机</t>
   </si>
   <si>
-    <t>超过百米的海上风力发电机的叶片采用了具有密度 小、强度高、耐腐蚀、抗疲劳等优异性能的碳纤维材料  （图 6.4-4）</t>
+    <t>超过百米的海上风力发电机的叶片采用了具有密度小、强度高、耐腐蚀、抗疲劳等优异性能的碳纤维材料（图 6.4-4）。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_06_04_03</t>
@@ -3629,7 +3617,7 @@
     <t>我国是世界上冶铁业出现较早</t>
   </si>
   <si>
-    <t>我国是世界上冶铁业出现较早的国家之一。春 秋战国时代，由铁制作的农具、手工工具及各种兵 器得以广泛应用</t>
+    <t>我国是世界上冶铁业出现较早的国家之一。春秋战国时代，由铁制作的农具、手工工具及各种兵器得以广泛应用。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_06_04_04</t>
@@ -3638,7 +3626,7 @@
     <t>我国自主研发的“手撕钢”</t>
   </si>
   <si>
-    <t>随着我国工业技术的发展，目前，我国自主研发的 “手撕钢”比纸还要薄（图 6.4-6） ，被不断应用到许多高新技术领域。 20 世纪，各种新材料层出不穷</t>
+    <t>随着我国工业技术的发展，目前，我国自主研发的 “手撕钢”比纸还要薄（图 6.4-6） ，被不断应用到许多高新技术领域。 20 世纪，各种新材料层出不穷。</t>
   </si>
   <si>
     <t>EV_PEP8U_PHYSICS_06_04_05</t>
@@ -11056,7 +11044,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="30.6634615384615" customWidth="1"/>
@@ -11648,48 +11636,48 @@
         <v>1046</v>
       </c>
       <c r="C23">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>990</v>
+        <v>963</v>
       </c>
       <c r="E23" t="s">
         <v>1047</v>
       </c>
       <c r="F23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="G23" t="s">
-        <v>1048</v>
+        <v>966</v>
       </c>
       <c r="H23" t="s">
-        <v>1049</v>
+        <v>967</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C24">
+        <v>71</v>
+      </c>
+      <c r="D24" t="s">
+        <v>990</v>
+      </c>
+      <c r="E24" t="s">
         <v>1050</v>
       </c>
-      <c r="C24">
-        <v>68</v>
-      </c>
-      <c r="D24" t="s">
-        <v>963</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>1051</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>1052</v>
       </c>
-      <c r="G24" t="s">
-        <v>966</v>
-      </c>
       <c r="H24" t="s">
-        <v>967</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -11697,25 +11685,25 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C25">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>990</v>
+        <v>963</v>
       </c>
       <c r="E25" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F25" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="G25" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H25" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -11723,51 +11711,51 @@
         <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C26">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="E26" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F26" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="G26" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H26" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C27">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="E27" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F27" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G27" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H27" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -11775,51 +11763,51 @@
         <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C28">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
         <v>963</v>
       </c>
       <c r="E28" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F28" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="G28" t="s">
-        <v>1071</v>
+        <v>1016</v>
       </c>
       <c r="H28" t="s">
-        <v>1072</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C29">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
         <v>963</v>
       </c>
       <c r="E29" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F29" t="s">
         <v>1074</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>1075</v>
       </c>
-      <c r="G29" t="s">
-        <v>1016</v>
-      </c>
       <c r="H29" t="s">
-        <v>1017</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -11827,77 +11815,77 @@
         <v>48</v>
       </c>
       <c r="B30" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C30">
+        <v>83</v>
+      </c>
+      <c r="D30" t="s">
+        <v>990</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H30" t="s">
         <v>1076</v>
-      </c>
-      <c r="C30">
-        <v>82</v>
-      </c>
-      <c r="D30" t="s">
-        <v>963</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F30" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G30" t="s">
-        <v>1079</v>
-      </c>
-      <c r="H30" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B31" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C31">
+        <v>91</v>
+      </c>
+      <c r="D31" t="s">
+        <v>945</v>
+      </c>
+      <c r="E31" t="s">
         <v>1081</v>
       </c>
-      <c r="C31">
-        <v>83</v>
-      </c>
-      <c r="D31" t="s">
-        <v>990</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>1082</v>
       </c>
-      <c r="F31" t="s">
-        <v>1083</v>
-      </c>
       <c r="G31" t="s">
-        <v>1079</v>
+        <v>948</v>
       </c>
       <c r="H31" t="s">
-        <v>1080</v>
+        <v>949</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C32">
+        <v>96</v>
+      </c>
+      <c r="D32" t="s">
+        <v>963</v>
+      </c>
+      <c r="E32" t="s">
         <v>1084</v>
       </c>
-      <c r="C32">
-        <v>91</v>
-      </c>
-      <c r="D32" t="s">
-        <v>945</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>1085</v>
       </c>
-      <c r="F32" t="s">
-        <v>1086</v>
-      </c>
       <c r="G32" t="s">
-        <v>948</v>
+        <v>981</v>
       </c>
       <c r="H32" t="s">
-        <v>949</v>
+        <v>982</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -11905,51 +11893,51 @@
         <v>54</v>
       </c>
       <c r="B33" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C33">
+        <v>97</v>
+      </c>
+      <c r="D33" t="s">
+        <v>957</v>
+      </c>
+      <c r="E33" t="s">
         <v>1087</v>
       </c>
-      <c r="C33">
-        <v>96</v>
-      </c>
-      <c r="D33" t="s">
-        <v>963</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>1088</v>
       </c>
-      <c r="F33" t="s">
-        <v>1089</v>
-      </c>
       <c r="G33" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="H33" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C34">
+        <v>100</v>
+      </c>
+      <c r="D34" t="s">
+        <v>945</v>
+      </c>
+      <c r="E34" t="s">
         <v>1090</v>
       </c>
-      <c r="C34">
-        <v>97</v>
-      </c>
-      <c r="D34" t="s">
-        <v>957</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>1091</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>1092</v>
       </c>
-      <c r="G34" t="s">
-        <v>976</v>
-      </c>
       <c r="H34" t="s">
-        <v>977</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -11957,25 +11945,25 @@
         <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C35">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D35" t="s">
-        <v>945</v>
+        <v>963</v>
       </c>
       <c r="E35" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F35" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="G35" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H35" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -11983,77 +11971,77 @@
         <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C36">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
-        <v>963</v>
+        <v>945</v>
       </c>
       <c r="E36" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F36" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="G36" t="s">
-        <v>1101</v>
+        <v>948</v>
       </c>
       <c r="H36" t="s">
-        <v>1102</v>
+        <v>949</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B37" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C37">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
         <v>945</v>
       </c>
       <c r="E37" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F37" t="s">
         <v>1104</v>
       </c>
-      <c r="F37" t="s">
-        <v>1105</v>
-      </c>
       <c r="G37" t="s">
-        <v>948</v>
+        <v>1092</v>
       </c>
       <c r="H37" t="s">
-        <v>949</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C38">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D38" t="s">
         <v>945</v>
       </c>
       <c r="E38" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F38" t="s">
         <v>1107</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>1108</v>
       </c>
-      <c r="G38" t="s">
-        <v>1096</v>
-      </c>
       <c r="H38" t="s">
-        <v>1097</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -12061,25 +12049,25 @@
         <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C39">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
-        <v>945</v>
+        <v>963</v>
       </c>
       <c r="E39" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F39" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="G39" t="s">
-        <v>1112</v>
+        <v>981</v>
       </c>
       <c r="H39" t="s">
-        <v>1113</v>
+        <v>982</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -12087,51 +12075,51 @@
         <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C40">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D40" t="s">
         <v>963</v>
       </c>
       <c r="E40" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F40" t="s">
         <v>1115</v>
       </c>
-      <c r="F40" t="s">
-        <v>1116</v>
-      </c>
       <c r="G40" t="s">
-        <v>981</v>
+        <v>1036</v>
       </c>
       <c r="H40" t="s">
-        <v>982</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B41" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C41">
+        <v>117</v>
+      </c>
+      <c r="D41" t="s">
+        <v>945</v>
+      </c>
+      <c r="E41" t="s">
         <v>1117</v>
       </c>
-      <c r="C41">
-        <v>110</v>
-      </c>
-      <c r="D41" t="s">
-        <v>963</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>1118</v>
       </c>
-      <c r="F41" t="s">
-        <v>1119</v>
-      </c>
       <c r="G41" t="s">
-        <v>1036</v>
+        <v>948</v>
       </c>
       <c r="H41" t="s">
-        <v>1037</v>
+        <v>949</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -12139,51 +12127,51 @@
         <v>64</v>
       </c>
       <c r="B42" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C42">
         <v>117</v>
       </c>
       <c r="D42" t="s">
-        <v>945</v>
+        <v>963</v>
       </c>
       <c r="E42" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F42" t="s">
         <v>1121</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>1122</v>
       </c>
-      <c r="G42" t="s">
-        <v>948</v>
-      </c>
       <c r="H42" t="s">
-        <v>949</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B43" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C43">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D43" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="E43" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F43" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G43" t="s">
-        <v>1126</v>
+        <v>976</v>
       </c>
       <c r="H43" t="s">
-        <v>1127</v>
+        <v>977</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -12191,19 +12179,19 @@
         <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C44">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D44" t="s">
         <v>957</v>
       </c>
       <c r="E44" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F44" t="s">
         <v>1129</v>
-      </c>
-      <c r="F44" t="s">
-        <v>1130</v>
       </c>
       <c r="G44" t="s">
         <v>976</v>
@@ -12214,16 +12202,16 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B45" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C45">
+        <v>123</v>
+      </c>
+      <c r="D45" t="s">
         <v>1131</v>
-      </c>
-      <c r="C45">
-        <v>119</v>
-      </c>
-      <c r="D45" t="s">
-        <v>957</v>
       </c>
       <c r="E45" t="s">
         <v>1132</v>
@@ -12232,36 +12220,36 @@
         <v>1133</v>
       </c>
       <c r="G45" t="s">
-        <v>976</v>
+        <v>1134</v>
       </c>
       <c r="H45" t="s">
-        <v>977</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="C46">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D46" t="s">
-        <v>1135</v>
+        <v>963</v>
       </c>
       <c r="E46" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="F46" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="G46" t="s">
-        <v>1138</v>
+        <v>981</v>
       </c>
       <c r="H46" t="s">
-        <v>1139</v>
+        <v>982</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -12269,19 +12257,19 @@
         <v>70</v>
       </c>
       <c r="B47" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C47">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D47" t="s">
         <v>963</v>
       </c>
       <c r="E47" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F47" t="s">
         <v>1141</v>
-      </c>
-      <c r="F47" t="s">
-        <v>1142</v>
       </c>
       <c r="G47" t="s">
         <v>981</v>
@@ -12292,28 +12280,28 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B48" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C48">
+        <v>133</v>
+      </c>
+      <c r="D48" t="s">
+        <v>990</v>
+      </c>
+      <c r="E48" t="s">
         <v>1143</v>
       </c>
-      <c r="C48">
-        <v>129</v>
-      </c>
-      <c r="D48" t="s">
-        <v>963</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>1144</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>1145</v>
       </c>
-      <c r="G48" t="s">
-        <v>981</v>
-      </c>
       <c r="H48" t="s">
-        <v>982</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -12321,25 +12309,25 @@
         <v>72</v>
       </c>
       <c r="B49" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C49">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D49" t="s">
-        <v>990</v>
+        <v>945</v>
       </c>
       <c r="E49" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="F49" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="G49" t="s">
-        <v>1149</v>
+        <v>948</v>
       </c>
       <c r="H49" t="s">
-        <v>1150</v>
+        <v>949</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -12347,7 +12335,7 @@
         <v>72</v>
       </c>
       <c r="B50" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C50">
         <v>134</v>
@@ -12356,16 +12344,16 @@
         <v>945</v>
       </c>
       <c r="E50" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F50" t="s">
         <v>1152</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>1153</v>
       </c>
-      <c r="G50" t="s">
-        <v>948</v>
-      </c>
       <c r="H50" t="s">
-        <v>949</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -12373,51 +12361,51 @@
         <v>72</v>
       </c>
       <c r="B51" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C51">
         <v>134</v>
       </c>
       <c r="D51" t="s">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="E51" t="s">
-        <v>1155</v>
+        <v>587</v>
       </c>
       <c r="F51" t="s">
         <v>1156</v>
       </c>
       <c r="G51" t="s">
-        <v>1157</v>
+        <v>960</v>
       </c>
       <c r="H51" t="s">
-        <v>1158</v>
+        <v>961</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B52" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C52">
+        <v>139</v>
+      </c>
+      <c r="D52" t="s">
+        <v>945</v>
+      </c>
+      <c r="E52" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F52" t="s">
         <v>1159</v>
       </c>
-      <c r="C52">
-        <v>134</v>
-      </c>
-      <c r="D52" t="s">
-        <v>957</v>
-      </c>
-      <c r="E52" t="s">
-        <v>587</v>
-      </c>
-      <c r="F52" t="s">
-        <v>1160</v>
-      </c>
       <c r="G52" t="s">
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="H52" t="s">
-        <v>961</v>
+        <v>949</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -12425,25 +12413,25 @@
         <v>76</v>
       </c>
       <c r="B53" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C53">
+        <v>142</v>
+      </c>
+      <c r="D53" t="s">
+        <v>951</v>
+      </c>
+      <c r="E53" t="s">
         <v>1161</v>
       </c>
-      <c r="C53">
-        <v>139</v>
-      </c>
-      <c r="D53" t="s">
-        <v>945</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>1162</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>1163</v>
       </c>
-      <c r="G53" t="s">
-        <v>948</v>
-      </c>
       <c r="H53" t="s">
-        <v>949</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -12451,51 +12439,51 @@
         <v>76</v>
       </c>
       <c r="B54" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="C54">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D54" t="s">
         <v>951</v>
       </c>
       <c r="E54" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="F54" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="G54" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="H54" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B55" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C55">
+        <v>145</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E55" t="s">
         <v>1169</v>
       </c>
-      <c r="C55">
-        <v>143</v>
-      </c>
-      <c r="D55" t="s">
-        <v>951</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>1170</v>
       </c>
-      <c r="F55" t="s">
-        <v>1171</v>
-      </c>
       <c r="G55" t="s">
-        <v>1167</v>
+        <v>966</v>
       </c>
       <c r="H55" t="s">
-        <v>1168</v>
+        <v>967</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -12503,51 +12491,51 @@
         <v>78</v>
       </c>
       <c r="B56" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C56">
+        <v>147</v>
+      </c>
+      <c r="D56" t="s">
+        <v>963</v>
+      </c>
+      <c r="E56" t="s">
         <v>1172</v>
       </c>
-      <c r="C56">
-        <v>145</v>
-      </c>
-      <c r="D56" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>1173</v>
       </c>
-      <c r="F56" t="s">
-        <v>1174</v>
-      </c>
       <c r="G56" t="s">
-        <v>966</v>
+        <v>1075</v>
       </c>
       <c r="H56" t="s">
-        <v>967</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C57">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D57" t="s">
         <v>963</v>
       </c>
       <c r="E57" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F57" t="s">
         <v>1176</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>1177</v>
       </c>
-      <c r="G57" t="s">
-        <v>1079</v>
-      </c>
       <c r="H57" t="s">
-        <v>1080</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -12555,51 +12543,51 @@
         <v>80</v>
       </c>
       <c r="B58" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="C58">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D58" t="s">
-        <v>963</v>
+        <v>945</v>
       </c>
       <c r="E58" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="F58" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="G58" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H58" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C59">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D59" t="s">
-        <v>945</v>
+        <v>963</v>
       </c>
       <c r="E59" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="F59" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="G59" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H59" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -12607,25 +12595,25 @@
         <v>82</v>
       </c>
       <c r="B60" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C60">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D60" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="E60" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="F60" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="G60" t="s">
-        <v>1191</v>
+        <v>1097</v>
       </c>
       <c r="H60" t="s">
-        <v>1192</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -12633,25 +12621,25 @@
         <v>82</v>
       </c>
       <c r="B61" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C61">
+        <v>155</v>
+      </c>
+      <c r="D61" t="s">
+        <v>945</v>
+      </c>
+      <c r="E61" t="s">
         <v>1193</v>
       </c>
-      <c r="C61">
-        <v>154</v>
-      </c>
-      <c r="D61" t="s">
-        <v>957</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>1194</v>
       </c>
-      <c r="F61" t="s">
-        <v>1195</v>
-      </c>
       <c r="G61" t="s">
-        <v>1101</v>
+        <v>948</v>
       </c>
       <c r="H61" t="s">
-        <v>1102</v>
+        <v>949</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -12659,25 +12647,25 @@
         <v>82</v>
       </c>
       <c r="B62" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C62">
         <v>155</v>
       </c>
       <c r="D62" t="s">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="E62" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F62" t="s">
         <v>1197</v>
       </c>
-      <c r="F62" t="s">
-        <v>1198</v>
-      </c>
       <c r="G62" t="s">
-        <v>948</v>
+        <v>1062</v>
       </c>
       <c r="H62" t="s">
-        <v>949</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -12685,50 +12673,24 @@
         <v>82</v>
       </c>
       <c r="B63" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C63">
+        <v>156</v>
+      </c>
+      <c r="D63" t="s">
+        <v>945</v>
+      </c>
+      <c r="E63" t="s">
         <v>1199</v>
       </c>
-      <c r="C63">
-        <v>155</v>
-      </c>
-      <c r="D63" t="s">
-        <v>957</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>1200</v>
       </c>
-      <c r="F63" t="s">
-        <v>1201</v>
-      </c>
       <c r="G63" t="s">
-        <v>1066</v>
+        <v>1003</v>
       </c>
       <c r="H63" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" t="s">
-        <v>82</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C64">
-        <v>156</v>
-      </c>
-      <c r="D64" t="s">
-        <v>945</v>
-      </c>
-      <c r="E64" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F64" t="s">
-        <v>1204</v>
-      </c>
-      <c r="G64" t="s">
-        <v>1003</v>
-      </c>
-      <c r="H64" t="s">
         <v>1004</v>
       </c>
     </row>
@@ -12754,276 +12716,276 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E1" t="s">
         <v>1205</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>1206</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E2" t="s">
         <v>1211</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F2" t="s">
         <v>1212</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="B3" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E3" t="s">
         <v>1213</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>1214</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="B4" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C4" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="D4" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="E4" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="F4" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="B5" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C5" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="D5" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="E5" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="F5" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="B6" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C6" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E6" t="s">
         <v>1221</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>1222</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1225</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="B7" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C7" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="D7" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="E7" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="F7" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="B8" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C8" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="D8" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="E8" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="F8" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="B9" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C9" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E9" t="s">
         <v>1229</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>1230</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1233</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="B10" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C10" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="D10" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="E10" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="F10" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="B11" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="C11" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="D11" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="E11" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="F11" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E12" t="s">
         <v>1237</v>
       </c>
-      <c r="B12" t="s">
+      <c r="F12" t="s">
         <v>1238</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1240</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1241</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="B13" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="C13" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E13" t="s">
         <v>1239</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>1240</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1243</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="B14" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="C14" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="D14" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="E14" t="s">
         <v>1016</v>
@@ -13034,296 +12996,296 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="B15" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="C15" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="D15" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="E15" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="F15" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="B16" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="C16" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E16" t="s">
         <v>1245</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>1246</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1249</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="B17" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="C17" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="D17" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="E17" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="F17" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="B18" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="C18" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E18" t="s">
         <v>1251</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>1252</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1255</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="B19" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="C19" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="D19" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="E19" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="F19" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E20" t="s">
         <v>1257</v>
       </c>
-      <c r="B20" t="s">
+      <c r="F20" t="s">
         <v>1258</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1259</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1260</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1261</v>
-      </c>
-      <c r="F20" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="B21" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C21" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E21" t="s">
         <v>1259</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>1260</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1263</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="B22" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C22" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="D22" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="E22" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="F22" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="B23" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C23" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="D23" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="E23" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="F23" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="B24" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C24" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E24" t="s">
         <v>1267</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>1268</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1271</v>
-      </c>
-      <c r="F24" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="B25" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C25" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="D25" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="E25" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="F25" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="B26" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C26" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="D26" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="E26" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="F26" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="B27" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C27" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E27" t="s">
         <v>1275</v>
       </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
         <v>1276</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1279</v>
-      </c>
-      <c r="F27" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="B28" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C28" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="D28" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="E28" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="F28" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="B29" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="C29" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="D29" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="E29" t="s">
         <v>948</v>
@@ -13334,176 +13296,176 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E30" t="s">
         <v>1281</v>
       </c>
-      <c r="B30" t="s">
+      <c r="F30" t="s">
         <v>1282</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1283</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1284</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1285</v>
-      </c>
-      <c r="F30" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="B31" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="C31" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E31" t="s">
         <v>1283</v>
       </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
         <v>1284</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1287</v>
-      </c>
-      <c r="F31" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="B32" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="C32" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="D32" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="E32" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="F32" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="B33" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="C33" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E33" t="s">
         <v>1289</v>
       </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
         <v>1290</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1293</v>
-      </c>
-      <c r="F33" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="B34" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="C34" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="D34" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="E34" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="F34" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="B35" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="C35" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="D35" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="E35" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="F35" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="B36" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="C36" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E36" t="s">
         <v>1297</v>
       </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
         <v>1298</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1301</v>
-      </c>
-      <c r="F36" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="B37" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="C37" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="D37" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="E37" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="F37" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B38" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C38" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="D38" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="E38" t="s">
         <v>981</v>
@@ -13514,236 +13476,236 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E39" t="s">
         <v>1305</v>
       </c>
-      <c r="B39" t="s">
+      <c r="F39" t="s">
         <v>1306</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1307</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1308</v>
-      </c>
-      <c r="E39" t="s">
-        <v>1309</v>
-      </c>
-      <c r="F39" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B40" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C40" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E40" t="s">
         <v>1307</v>
       </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>1308</v>
-      </c>
-      <c r="E40" t="s">
-        <v>1311</v>
-      </c>
-      <c r="F40" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B41" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C41" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D41" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="E41" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="F41" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B42" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C42" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E42" t="s">
         <v>1313</v>
       </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
         <v>1314</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1317</v>
-      </c>
-      <c r="F42" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B43" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C43" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D43" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="E43" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="F43" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B44" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C44" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="D44" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="E44" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="F44" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B45" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C45" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E45" t="s">
         <v>1321</v>
       </c>
-      <c r="D45" t="s">
+      <c r="F45" t="s">
         <v>1322</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1325</v>
-      </c>
-      <c r="F45" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B46" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C46" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="D46" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="E46" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="F46" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E47" t="s">
         <v>1329</v>
       </c>
-      <c r="B47" t="s">
+      <c r="F47" t="s">
         <v>1330</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1331</v>
-      </c>
-      <c r="D47" t="s">
-        <v>1332</v>
-      </c>
-      <c r="E47" t="s">
-        <v>1333</v>
-      </c>
-      <c r="F47" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B48" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C48" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E48" t="s">
         <v>1331</v>
       </c>
-      <c r="D48" t="s">
+      <c r="F48" t="s">
         <v>1332</v>
-      </c>
-      <c r="E48" t="s">
-        <v>1335</v>
-      </c>
-      <c r="F48" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B49" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C49" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="D49" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="E49" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="F49" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B50" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C50" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D50" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="E50" t="s">
         <v>966</v>
@@ -13754,116 +13716,116 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B51" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C51" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D51" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="E51" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="F51" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B52" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C52" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E52" t="s">
         <v>1339</v>
       </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
         <v>1340</v>
-      </c>
-      <c r="E52" t="s">
-        <v>1343</v>
-      </c>
-      <c r="F52" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B53" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C53" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="D53" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="E53" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="F53" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B54" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C54" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E54" t="s">
         <v>1345</v>
       </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
         <v>1346</v>
-      </c>
-      <c r="E54" t="s">
-        <v>1349</v>
-      </c>
-      <c r="F54" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B55" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C55" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="D55" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="E55" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="F55" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B56" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C56" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="D56" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="E56" t="s">
         <v>976</v>
@@ -13874,762 +13836,762 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B57" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C57" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="D57" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="E57" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="F57" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B58" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C58" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E58" t="s">
         <v>1353</v>
       </c>
-      <c r="D58" t="s">
+      <c r="F58" t="s">
         <v>1354</v>
-      </c>
-      <c r="E58" t="s">
-        <v>1357</v>
-      </c>
-      <c r="F58" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E59" t="s">
         <v>1359</v>
       </c>
-      <c r="B59" t="s">
+      <c r="F59" t="s">
         <v>1360</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1361</v>
-      </c>
-      <c r="D59" t="s">
-        <v>1362</v>
-      </c>
-      <c r="E59" t="s">
-        <v>1363</v>
-      </c>
-      <c r="F59" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="B60" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C60" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E60" t="s">
         <v>1361</v>
       </c>
-      <c r="D60" t="s">
+      <c r="F60" t="s">
         <v>1362</v>
-      </c>
-      <c r="E60" t="s">
-        <v>1365</v>
-      </c>
-      <c r="F60" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="B61" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C61" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D61" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="E61" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="F61" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="B62" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C62" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="D62" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E62" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="F62" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="B63" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C63" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E63" t="s">
         <v>1369</v>
       </c>
-      <c r="D63" t="s">
+      <c r="F63" t="s">
         <v>1370</v>
-      </c>
-      <c r="E63" t="s">
-        <v>1373</v>
-      </c>
-      <c r="F63" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="B64" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C64" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="D64" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E64" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="F64" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="B65" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C65" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="D65" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="E65" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="F65" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="B66" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C66" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E66" t="s">
         <v>1377</v>
       </c>
-      <c r="D66" t="s">
+      <c r="F66" t="s">
         <v>1378</v>
-      </c>
-      <c r="E66" t="s">
-        <v>1381</v>
-      </c>
-      <c r="F66" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="B67" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C67" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="D67" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="E67" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="F67" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D68" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E68" t="s">
         <v>1385</v>
       </c>
-      <c r="B68" t="s">
+      <c r="F68" t="s">
         <v>1386</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1387</v>
-      </c>
-      <c r="D68" t="s">
-        <v>1388</v>
-      </c>
-      <c r="E68" t="s">
-        <v>1389</v>
-      </c>
-      <c r="F68" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B69" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="C69" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E69" t="s">
         <v>1387</v>
       </c>
-      <c r="D69" t="s">
+      <c r="F69" t="s">
         <v>1388</v>
-      </c>
-      <c r="E69" t="s">
-        <v>1391</v>
-      </c>
-      <c r="F69" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B70" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="C70" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="D70" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="E70" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="F70" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B71" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="C71" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="D71" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="E71" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="F71" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B72" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="C72" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D72" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E72" t="s">
         <v>1395</v>
       </c>
-      <c r="D72" t="s">
+      <c r="F72" t="s">
         <v>1396</v>
-      </c>
-      <c r="E72" t="s">
-        <v>1399</v>
-      </c>
-      <c r="F72" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B73" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="C73" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="D73" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="E73" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="F73" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B74" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="C74" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="D74" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="E74" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="F74" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B75" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="C75" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E75" t="s">
         <v>1403</v>
       </c>
-      <c r="D75" t="s">
+      <c r="F75" t="s">
         <v>1404</v>
-      </c>
-      <c r="E75" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F75" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B76" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="C76" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="D76" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="E76" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="F76" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E77" t="s">
         <v>1411</v>
       </c>
-      <c r="B77" t="s">
+      <c r="F77" t="s">
         <v>1412</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D77" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E77" t="s">
-        <v>1415</v>
-      </c>
-      <c r="F77" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B78" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="C78" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D78" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E78" t="s">
         <v>1413</v>
       </c>
-      <c r="D78" t="s">
+      <c r="F78" t="s">
         <v>1414</v>
-      </c>
-      <c r="E78" t="s">
-        <v>1417</v>
-      </c>
-      <c r="F78" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B79" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="C79" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="D79" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="E79" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="F79" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B80" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="C80" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="D80" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="E80" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
       <c r="F80" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B81" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="C81" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D81" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E81" t="s">
         <v>1421</v>
       </c>
-      <c r="D81" t="s">
+      <c r="F81" t="s">
         <v>1422</v>
-      </c>
-      <c r="E81" t="s">
-        <v>1425</v>
-      </c>
-      <c r="F81" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B82" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="C82" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="D82" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="E82" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="F82" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B83" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="C83" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
       <c r="D83" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="E83" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
       <c r="F83" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B84" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="C84" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D84" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E84" t="s">
         <v>1429</v>
       </c>
-      <c r="D84" t="s">
+      <c r="F84" t="s">
         <v>1430</v>
-      </c>
-      <c r="E84" t="s">
-        <v>1433</v>
-      </c>
-      <c r="F84" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B85" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="C85" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
       <c r="D85" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="E85" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="F85" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D86" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E86" t="s">
         <v>1437</v>
       </c>
-      <c r="B86" t="s">
+      <c r="F86" t="s">
         <v>1438</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1439</v>
-      </c>
-      <c r="D86" t="s">
-        <v>1440</v>
-      </c>
-      <c r="E86" t="s">
-        <v>1441</v>
-      </c>
-      <c r="F86" t="s">
-        <v>1442</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="B87" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="C87" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D87" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E87" t="s">
         <v>1439</v>
       </c>
-      <c r="D87" t="s">
+      <c r="F87" t="s">
         <v>1440</v>
-      </c>
-      <c r="E87" t="s">
-        <v>1443</v>
-      </c>
-      <c r="F87" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="B88" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="C88" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="D88" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="E88" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="F88" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="B89" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="C89" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="D89" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="E89" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="F89" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="B90" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="C90" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D90" t="s">
+        <v>1444</v>
+      </c>
+      <c r="E90" t="s">
         <v>1447</v>
       </c>
-      <c r="D90" t="s">
+      <c r="F90" t="s">
         <v>1448</v>
-      </c>
-      <c r="E90" t="s">
-        <v>1451</v>
-      </c>
-      <c r="F90" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="B91" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="C91" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="D91" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="E91" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="F91" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="B92" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="C92" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="D92" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="E92" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="F92" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="B93" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="C93" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D93" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E93" t="s">
         <v>1453</v>
       </c>
-      <c r="D93" t="s">
+      <c r="F93" t="s">
         <v>1454</v>
-      </c>
-      <c r="E93" t="s">
-        <v>1457</v>
-      </c>
-      <c r="F93" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="B94" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="C94" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="D94" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="E94" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="F94" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
     </row>
   </sheetData>
